--- a/SourceData/Datas/craft_recipe.xlsx
+++ b/SourceData/Datas/craft_recipe.xlsx
@@ -1031,7 +1031,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:J13"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col width="8.54545454545454" customWidth="1" min="1" max="1"/>
@@ -1084,6 +1084,16 @@
           <t>sort</t>
         </is>
       </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>unlock_quest</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>unlock_mode</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1133,6 +1143,16 @@
           <t>int</t>
         </is>
       </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1175,6 +1195,16 @@
           <t>c</t>
         </is>
       </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1217,6 +1247,16 @@
           <t>排序</t>
         </is>
       </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>解锁任务ID</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>解锁模式 reached|completed|空=常驻</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="B6" t="inlineStr">
@@ -1248,6 +1288,14 @@
       <c r="H6" t="n">
         <v>10</v>
       </c>
+      <c r="I6" t="n">
+        <v>1003</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>reached</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="B7" t="inlineStr">
@@ -1279,98 +1327,247 @@
       <c r="H7" t="n">
         <v>20</v>
       </c>
+      <c r="I7" t="n">
+        <v>1003</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="B8" t="inlineStr">
         <is>
-          <t>wood_bundle</t>
+          <t>can_basic</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>精制木料</t>
+          <t>水壶</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>用草绳捆扎，多出一根可用木料</t>
+          <t>石片与泥土捏成的浇水壶</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>wood</t>
+          <t>can</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G8" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H8" t="n">
-        <v>30</v>
+        <v>25</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1031</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>reached</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="B9" t="inlineStr">
         <is>
-          <t>stone_pack</t>
+          <t>axe_basic</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>加固石料</t>
+          <t>斧头</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>泥土粘合碎石，得到更多石料</t>
+          <t>石刃裹草绳，能砍倒松树与橡树</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>stone</t>
+          <t>axe</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G9" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H9" t="n">
-        <v>40</v>
+        <v>26</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1032</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>reached</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="B10" t="inlineStr">
         <is>
+          <t>rod_basic</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>鱼竿</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>木杆缠草线，湖边抛竿用</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>rod</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" t="n">
+        <v>18</v>
+      </c>
+      <c r="H10" t="n">
+        <v>27</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1034</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>reached</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>wood_bundle</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>精制木料</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>用草绳捆扎，多出一根可用木料</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>wood</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>3</v>
+      </c>
+      <c r="G11" t="n">
+        <v>20</v>
+      </c>
+      <c r="H11" t="n">
+        <v>30</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1033</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>stone_pack</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>加固石料</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>泥土粘合碎石，得到更多石料</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>stone</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>2</v>
+      </c>
+      <c r="G12" t="n">
+        <v>22</v>
+      </c>
+      <c r="H12" t="n">
+        <v>40</v>
+      </c>
+      <c r="I12" t="n">
+        <v>1031</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" t="inlineStr">
+        <is>
           <t>fish_bait_seed</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>鱼肥种子</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>鱼骨与草料沤成的肥沃种子</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>seeds</t>
         </is>
       </c>
-      <c r="F10" t="n">
+      <c r="F13" t="n">
         <v>3</v>
       </c>
-      <c r="G10" t="n">
+      <c r="G13" t="n">
         <v>28</v>
       </c>
-      <c r="H10" t="n">
+      <c r="H13" t="n">
         <v>50</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1007</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/SourceData/Datas/craft_recipe.xlsx
+++ b/SourceData/Datas/craft_recipe.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowHeight="18400" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="craft_recipe" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="craft_recipe" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -1031,7 +1031,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J13"/>
+  <dimension ref="A1:J9"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col width="8.54545454545454" customWidth="1" min="1" max="1"/>
@@ -1300,74 +1300,74 @@
     <row r="7">
       <c r="B7" t="inlineStr">
         <is>
-          <t>seed_mix</t>
+          <t>can_basic</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>混合种子</t>
+          <t>水壶</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>泥土与草料拌成的种子袋</t>
+          <t>石片与泥土捏成的浇水壶</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>seeds</t>
+          <t>can</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G7" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H7" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="I7" t="n">
-        <v>1003</v>
+        <v>1031</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>reached</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="B8" t="inlineStr">
         <is>
-          <t>can_basic</t>
+          <t>axe_basic</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>水壶</t>
+          <t>斧头</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>石片与泥土捏成的浇水壶</t>
+          <t>石刃裹草绳，能砍倒松树与橡树</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>can</t>
+          <t>axe</t>
         </is>
       </c>
       <c r="F8" t="n">
         <v>1</v>
       </c>
       <c r="G8" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="H8" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I8" t="n">
-        <v>1031</v>
+        <v>1032</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -1378,22 +1378,22 @@
     <row r="9">
       <c r="B9" t="inlineStr">
         <is>
-          <t>axe_basic</t>
+          <t>rod_basic</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>斧头</t>
+          <t>鱼竿</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>石刃裹草绳，能砍倒松树与橡树</t>
+          <t>木杆缠草线，湖边抛竿用</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>axe</t>
+          <t>rod</t>
         </is>
       </c>
       <c r="F9" t="n">
@@ -1403,170 +1403,14 @@
         <v>18</v>
       </c>
       <c r="H9" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I9" t="n">
-        <v>1032</v>
+        <v>1034</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
           <t>reached</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>rod_basic</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>鱼竿</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>木杆缠草线，湖边抛竿用</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>rod</t>
-        </is>
-      </c>
-      <c r="F10" t="n">
-        <v>1</v>
-      </c>
-      <c r="G10" t="n">
-        <v>18</v>
-      </c>
-      <c r="H10" t="n">
-        <v>27</v>
-      </c>
-      <c r="I10" t="n">
-        <v>1034</v>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>reached</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>wood_bundle</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>精制木料</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>用草绳捆扎，多出一根可用木料</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>wood</t>
-        </is>
-      </c>
-      <c r="F11" t="n">
-        <v>3</v>
-      </c>
-      <c r="G11" t="n">
-        <v>20</v>
-      </c>
-      <c r="H11" t="n">
-        <v>30</v>
-      </c>
-      <c r="I11" t="n">
-        <v>1033</v>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>stone_pack</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>加固石料</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>泥土粘合碎石，得到更多石料</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>stone</t>
-        </is>
-      </c>
-      <c r="F12" t="n">
-        <v>2</v>
-      </c>
-      <c r="G12" t="n">
-        <v>22</v>
-      </c>
-      <c r="H12" t="n">
-        <v>40</v>
-      </c>
-      <c r="I12" t="n">
-        <v>1031</v>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>fish_bait_seed</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>鱼肥种子</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>鱼骨与草料沤成的肥沃种子</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>seeds</t>
-        </is>
-      </c>
-      <c r="F13" t="n">
-        <v>3</v>
-      </c>
-      <c r="G13" t="n">
-        <v>28</v>
-      </c>
-      <c r="H13" t="n">
-        <v>50</v>
-      </c>
-      <c r="I13" t="n">
-        <v>1007</v>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>completed</t>
         </is>
       </c>
     </row>
